--- a/nriss-patch-1/ig/all-profiles.xlsx
+++ b/nriss-patch-1/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T12:40:20+00:00</t>
+    <t>2026-07-21T13:21:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
